--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35938-2026 artfynd.xlsx
+++ b/artfynd/A 35938-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136479484</v>
       </c>
       <c r="B3" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
